--- a/docs/BibVik spreadsheet.xlsx
+++ b/docs/BibVik spreadsheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackbatist/Library/CloudStorage/Dropbox/obsidian/projects/BibVik/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackbatist/Library/CloudStorage/Dropbox/obsidian/projects/BibVik/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C07C44BC-4D3D-5B47-B89E-3D75FD74116D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B987E1F4-8DB0-AE4B-BF69-EAA7CA99D9AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41120" yWindow="880" windowWidth="51200" windowHeight="27920" xr2:uid="{FE0B43CD-D6A2-45BB-955D-06FC2D89C712}"/>
+    <workbookView xWindow="1500" yWindow="880" windowWidth="39620" windowHeight="25700" xr2:uid="{FE0B43CD-D6A2-45BB-955D-06FC2D89C712}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
   <si>
     <t>Year</t>
   </si>
@@ -162,6 +162,33 @@
   </si>
   <si>
     <t>Based on data reuse</t>
+  </si>
+  <si>
+    <t>1. Discourse, critical review, etc</t>
+  </si>
+  <si>
+    <t>2. Archeaometry</t>
+  </si>
+  <si>
+    <t>3. Built landscapes</t>
+  </si>
+  <si>
+    <t>4. Portable finds</t>
+  </si>
+  <si>
+    <t>5. Synthesis</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Methods</t>
+  </si>
+  <si>
+    <t>Sources of evidence</t>
+  </si>
+  <si>
+    <t>Burial</t>
   </si>
 </sst>
 </file>
@@ -301,37 +328,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -666,15 +691,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97611E59-DC5D-41E1-A5D2-E37EA52A9247}">
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AL3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.5" bestFit="1" customWidth="1"/>
@@ -691,7 +716,7 @@
     <col min="22" max="22" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="7" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6" style="3" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6" style="2" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="12.5" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="7.5" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="18.1640625" bestFit="1" customWidth="1"/>
@@ -699,156 +724,180 @@
     <col min="30" max="30" width="3.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="11" t="s">
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="V1" s="11"/>
-      <c r="W1" s="11"/>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="12" t="s">
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+      <c r="Z1" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="AA1" s="12"/>
-      <c r="AB1" s="12"/>
-      <c r="AC1" s="12"/>
-      <c r="AD1" s="12"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="S2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="T2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="U2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="V2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="W2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="X2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="Y2" s="7" t="s">
+      <c r="Y2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Z2" s="8" t="s">
+      <c r="Z2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="8" t="s">
+      <c r="AA2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="8" t="s">
+      <c r="AB2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="8" t="s">
+      <c r="AC2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="8" t="s">
+      <c r="AD2" s="7" t="s">
         <v>25</v>
       </c>
+      <c r="AF2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>33</v>
       </c>
       <c r="B3" s="1">
         <v>2020</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>38</v>
       </c>
       <c r="I3" t="s">
@@ -863,7 +912,7 @@
       <c r="V3" t="s">
         <v>32</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Y3" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AA3" t="s">
@@ -874,6 +923,18 @@
       </c>
       <c r="AD3" t="s">
         <v>41</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
